--- a/AAII_Financials/Quarterly/PSA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PSA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
   <si>
     <t>PSA</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1237800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1224600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1220300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1227700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1198900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1186800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1181800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1190600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1179700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1163300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1165000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1151000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1129300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1100200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1088500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1088100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1032000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>973400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>924300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>894900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>829300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>767300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>759000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>730700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>709300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>716100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>725800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>729300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>711000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>689000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>692500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>706400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>685500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>669900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>672300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>686400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>664300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>645500</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>651400</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>663100</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>323300</v>
+      </c>
+      <c r="E9" s="3">
         <v>316000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>309600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>307000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>296700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>308700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>290400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>296400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>281400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>328200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>291900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>294000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>283000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>293800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>259700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>277000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>255200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>261000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>236900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>236700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>218600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>228400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>205500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>217500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>225600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>218900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>189000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>212300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>207700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>204200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>160400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>195500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>191000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>192800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>151900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>190600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>182600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>182900</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>145200</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>178600</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>914500</v>
+      </c>
+      <c r="E10" s="3">
         <v>908500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>910800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>920800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>902200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>878100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>891400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>894200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>898300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>835100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>873100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>857000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>846300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>806500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>828800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>811100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>776800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>712400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>687400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>658200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>610700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>538900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>553500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>513200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>483700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>497200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>536800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>517000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>503300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>484800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>532100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>510900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>494500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>477100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>520400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>495800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>481700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>462600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>506200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>484500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,104 +1496,107 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2700</v>
+        <v>5600</v>
       </c>
       <c r="E14" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F14" s="3">
         <v>2200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-5200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1800</v>
       </c>
-      <c r="H14" s="3">
-        <v>4700</v>
-      </c>
       <c r="I14" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-3200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-2000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-5600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-2127800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-1400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>4100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>4800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>3700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-151600</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1592,8 +1612,8 @@
       <c r="AM14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
+      <c r="AN14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AO14" s="3">
         <v>0</v>
@@ -1601,130 +1621,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>287800</v>
+      </c>
+      <c r="E15" s="3">
         <v>290700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>295500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>290400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>283200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>282700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>280900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>280300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>283300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>285200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>287500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>238700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>222100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>221700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>226500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>220800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>218700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>222100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>205300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>188600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>172700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>146900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>141400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>138300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>137600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>135900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>134900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>129200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>126900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>121900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>121400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>124500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>119800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>118000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>120100</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>113300</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>110200</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>110900</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>111700</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>109400</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>660900</v>
+        <v>672100</v>
       </c>
       <c r="E17" s="3">
+        <v>658200</v>
+      </c>
+      <c r="F17" s="3">
         <v>656500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>651300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>628500</v>
       </c>
-      <c r="H17" s="3">
-        <v>643300</v>
-      </c>
       <c r="I17" s="3">
+        <v>642600</v>
+      </c>
+      <c r="J17" s="3">
         <v>630600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>630800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>613900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>634700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>602600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>553500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>524900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>532400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>519500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-1601500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>502700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>506200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>464400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>457000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>419100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>394900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>367500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>377100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>383500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>375800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>334300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>358400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>349900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>345600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>158600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>347500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>342100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>342300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>292500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>326300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>307700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>318900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>277100</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>310200</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>563700</v>
+        <v>565700</v>
       </c>
       <c r="E18" s="3">
+        <v>566400</v>
+      </c>
+      <c r="F18" s="3">
         <v>563900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>576400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>570400</v>
       </c>
-      <c r="H18" s="3">
-        <v>543500</v>
-      </c>
       <c r="I18" s="3">
+        <v>544300</v>
+      </c>
+      <c r="J18" s="3">
         <v>551200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>559900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>565800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>528600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>562400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>597600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>604400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>567800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>569000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2689600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>529300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>467200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>459900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>437900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>410200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>372400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>391500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>353600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>325800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>340300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>391500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>370900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>361100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>343400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>533900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>358900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>343400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>327600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>379800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>360200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>356600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>326600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>374300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>352900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,549 +2085,562 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-42600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>140500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>62800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-127200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>65400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-16700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-41800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>66300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-51500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>22300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-117900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>122600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>160600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>82200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>191900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>77400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>23500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>77100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-24900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-13500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>40500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>8300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>41100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>22600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>32500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>61900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>28800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>70300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>25000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>19300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>18400</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>42200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>897000</v>
+        <v>875100</v>
       </c>
       <c r="E21" s="3">
+        <v>899700</v>
+      </c>
+      <c r="F21" s="3">
         <v>864300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>872200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>713100</v>
       </c>
-      <c r="H21" s="3">
-        <v>763400</v>
-      </c>
       <c r="I21" s="3">
+        <v>764200</v>
+      </c>
+      <c r="J21" s="3">
         <v>959300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>774800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>865900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>855500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>783600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>887900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>830400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>767200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>677600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3033000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>908500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>771500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>857100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>703900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>606500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>596400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>508100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>478500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>467600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>516700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>534600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>541300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>510600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>497800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>717200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>512200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>533500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>470500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>519200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>474000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>466500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>456000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>528300</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>479700</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>84800</v>
+      </c>
+      <c r="E22" s="3">
         <v>80000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>81200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>79700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>71600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>72000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>72100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>74300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>73200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>67800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>68600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>58400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>38100</v>
-      </c>
-      <c r="P22" s="3">
-        <v>36100</v>
       </c>
       <c r="Q22" s="3">
         <v>36100</v>
       </c>
       <c r="R22" s="3">
+        <v>36100</v>
+      </c>
+      <c r="S22" s="3">
         <v>34100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>32900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>33100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>29800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>22000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>15300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>14200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>14300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>14100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>13600</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>12600</v>
       </c>
       <c r="AD22" s="3">
         <v>12600</v>
       </c>
       <c r="AE22" s="3">
+        <v>12600</v>
+      </c>
+      <c r="AF22" s="3">
         <v>12300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>5400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>8100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>8400</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>8100</v>
       </c>
       <c r="AK22" s="3">
         <v>8100</v>
       </c>
       <c r="AL22" s="3">
+        <v>8100</v>
+      </c>
+      <c r="AM22" s="3">
         <v>2400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>1100</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>1000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>900</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>505700</v>
+      </c>
+      <c r="E23" s="3">
         <v>530900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>495300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>517600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>364700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>412200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>617000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>435600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>523300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>513200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>444300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>619500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>583700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>523500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>414900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2778200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>656900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>516300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>622000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>491600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>411700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>434300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>352400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>325800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>315800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>367100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>387100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>399400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>371500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>367700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>590500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>379600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>405300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>344400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>391000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>358300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>355200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>344000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>415700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>369100</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-14700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3100</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -2662,8 +2708,11 @@
       <c r="AP24" s="3">
         <v>0</v>
       </c>
+      <c r="AQ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>502900</v>
+      </c>
+      <c r="E26" s="3">
         <v>529400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>510100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>514800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>361400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>410800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>618400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>433100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>521200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>511700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>441900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>616600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>581200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>520400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>414900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2778200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>656900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>516300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>622000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>491600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>411700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>434300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>352400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>325800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>315800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>367100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>387100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>399400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>371500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>367700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>590500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>379600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>405300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>344400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>391000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>358300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>355200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>344000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>415700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>369100</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>450300</v>
+      </c>
+      <c r="E27" s="3">
         <v>476800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>457000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>461400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>309000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>358200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>564400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>380700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>468400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>459200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>389700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>563200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>528300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>467600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>362600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2712200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>603400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>464100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>558100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>442300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>346200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>385800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>292200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>246900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>246100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>313100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>327300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>337400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>306400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>301700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>532700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>322700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>348300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>287800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>334100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>279700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>276700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>281100</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>352800</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>309000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E32" s="3">
         <v>42600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-140500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-62800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>127200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-65400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>16700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>41800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-66300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>51500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-22300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>117900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-122600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-160600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-82200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-191900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-77400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-23500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-77100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>24900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>13500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-40500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-8300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-41100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-22600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-32500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-61900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-28800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-70300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-19300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-18400</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-42200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-17400</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>500000</v>
+      </c>
+      <c r="E33" s="3">
         <v>526300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>507100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>511100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>358400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>407800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>614600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>430300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>518100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>508900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>439300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>613300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>578000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>517700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>362600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2712200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>603400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>464100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>558100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>442300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>346200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>385800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>292200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>246900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>246100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>313100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>327300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>337400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>306400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>301700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>532700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>322700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>348300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>287800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>334100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>279700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>276700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>281100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>352800</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>309000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>500000</v>
+      </c>
+      <c r="E35" s="3">
         <v>526300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>507100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>511100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>358400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>407800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>614600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>430300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>518100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>508900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>439300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>613300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>578000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>517700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>362600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2712200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>603400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>464100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>558100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>442300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>346200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>385800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>292200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>246900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>246100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>313100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>327300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>337400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>306400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>301700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>532700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>322700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>348300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>287800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>334100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>279700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>276700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>281100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>352800</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>309000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>259900</v>
+      </c>
+      <c r="E41" s="3">
         <v>134600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>318100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>296500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1104600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>287200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>447400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>599000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>542300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>271600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>370000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>629800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>651700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>695400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>775300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>883800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1013900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>940500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>734600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>958200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>480800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>159600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>257600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>294000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1268500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>718400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>409700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>541400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>360300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>218000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>361200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>432500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>338400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>363000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>433400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>694200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>358300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>120900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>183700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>57200</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,32 +4553,35 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>173300</v>
+      </c>
+      <c r="E43" s="3">
         <v>142500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>142100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>93700</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3">
         <v>10000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4507,8 +4600,8 @@
       <c r="P43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4585,8 +4678,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,13 +4803,16 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>7100</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
@@ -4751,8 +4850,8 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4829,53 +4928,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>440300</v>
+      </c>
+      <c r="E46" s="3">
         <v>277100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>460200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>390200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1104600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>287200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>457400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>599000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>573500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>302200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>400400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>660400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>682100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>725800</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4951,374 +5053,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>364800</v>
+      </c>
+      <c r="E47" s="3">
         <v>383900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>388600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>383600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>387900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>374100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>382500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>397500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>374200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>389000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>390200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>278100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>276800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>285700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>275800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>252600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>845900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>850600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>828800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>779300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>767900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>771100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>773000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>769900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>753400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>763200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>767800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>771200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>778500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>784300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>784000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>619400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>762200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>746300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>724200</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>726200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>715300</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>698700</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>689200</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>697000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18754100</v>
+      </c>
+      <c r="E48" s="3">
         <v>18679000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>18804600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18779800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>18430800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>18399300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>18360700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>18232200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>18274400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>18315900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18386700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>18265600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16163600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16041200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16038000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15835700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15545500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15422700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>15307000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13086400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12792000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10559700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10408600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9947300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9969900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>9959500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9807600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9718500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9598500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9495700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9442100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>9348400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>9255000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>9235000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>9230100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>9006000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>8959600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>8929700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>8922600</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>8780700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>228000</v>
+      </c>
+      <c r="E49" s="3">
         <v>233200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>251600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>269600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>253500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>263200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>282200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>294500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>320800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>351500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>387300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>414300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>212000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>219700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>232500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>239800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>249700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>271100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>302900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>258900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>265500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>205100</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>204700</v>
       </c>
       <c r="Z49" s="3">
         <v>204700</v>
       </c>
       <c r="AA49" s="3">
+        <v>204700</v>
+      </c>
+      <c r="AB49" s="3">
         <v>206900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>209400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>205900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>211500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>210200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>210500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>209900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>209300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>207400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>210700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>215000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>205900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>207200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>209600</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>212700</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>212500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,53 +5678,56 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>330500</v>
+      </c>
+      <c r="E52" s="3">
         <v>277200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>303600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>291300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>364600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>291700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>272200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>280000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>246000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>258800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>244700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>257400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>225900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>235400</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5683,8 +5803,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20117700</v>
+      </c>
+      <c r="E54" s="3">
         <v>19850400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20208600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>20114300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20541500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19615400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19754900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19803200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19788800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19617400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19809200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19875700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17560300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17507800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>17552300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17450900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17862900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17698800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17380900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>15284700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14490400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>11981700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>11816500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11385100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12358100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11825900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11365400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11413900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11113300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>10875000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>10928300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>10747900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>10693000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>10685500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>10732900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>10765700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>10365700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>10083900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>10130300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>9865800</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,8 +6145,9 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -6059,8 +6190,8 @@
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -6137,35 +6268,38 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1350100</v>
+      </c>
+      <c r="E58" s="3">
         <v>975100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1154100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>783800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1183700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1161100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>650700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>399300</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -6259,17 +6393,20 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>5300</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F59" s="3" t="s">
         <v>8</v>
       </c>
@@ -6303,131 +6440,134 @@
       <c r="P59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R59" s="3">
         <v>514700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>589700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>473600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>454000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>482100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>474200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>406600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>368300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>394700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>433500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>395000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>357000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>383300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>445000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>410700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>374200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>371300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>410000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>351300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>326800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>337200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>380400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>322900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>294500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>297900</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>345700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2001800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1473500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1701500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1448200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1808600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1681600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1238900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1018700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>584600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>504200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>599000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>644300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>507600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>470400</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6503,130 +6643,136 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8830100</v>
+      </c>
+      <c r="E61" s="3">
         <v>9057200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9165300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9259000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9256500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8263500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8702300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9074400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9400500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9067900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9103300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9029600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6894200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6899300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6870800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6740500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7340900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7441700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7475300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5773200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5320600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2996100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2845000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2499600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2457900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2438700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1902500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2179900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1908100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1406200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1412300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1417900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1420800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1442900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1431300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1425900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>880800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>395900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>390700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>430900</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6669,8 +6815,8 @@
       <c r="P62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -6747,8 +6893,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10831900</v>
+      </c>
+      <c r="E66" s="3">
         <v>10530700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10866800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10707200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11065100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9945100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9941300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10093200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9985100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9572100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9702300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9673900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7401800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7369700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7478900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7423700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7908100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8000100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8045700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6267300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5746800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3383800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3257700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2951000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3365400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2812800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2302500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2639700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2344400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1805200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1808800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1852800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1797200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1794500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1792900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1829500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1226600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>720400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>718400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>806100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7580,40 +7748,40 @@
         <v>4350000</v>
       </c>
       <c r="U70" s="3">
+        <v>4350000</v>
+      </c>
+      <c r="V70" s="3">
         <v>4100000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>4015000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>3871300</v>
-      </c>
-      <c r="X70" s="3">
-        <v>3792500</v>
       </c>
       <c r="Y70" s="3">
         <v>3792500</v>
       </c>
       <c r="Z70" s="3">
+        <v>3792500</v>
+      </c>
+      <c r="AA70" s="3">
         <v>3640000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>4135000</v>
-      </c>
-      <c r="AB70" s="3">
-        <v>4065000</v>
       </c>
       <c r="AC70" s="3">
         <v>4065000</v>
       </c>
       <c r="AD70" s="3">
+        <v>4065000</v>
+      </c>
+      <c r="AE70" s="3">
         <v>3766300</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>3737500</v>
-      </c>
-      <c r="AF70" s="3">
-        <v>4025000</v>
       </c>
       <c r="AG70" s="3">
         <v>4025000</v>
@@ -7634,19 +7802,22 @@
         <v>4025000</v>
       </c>
       <c r="AM70" s="3">
+        <v>4025000</v>
+      </c>
+      <c r="AN70" s="3">
         <v>4187500</v>
-      </c>
-      <c r="AN70" s="3">
-        <v>4367500</v>
       </c>
       <c r="AO70" s="3">
         <v>4367500</v>
       </c>
       <c r="AP70" s="3">
+        <v>4367500</v>
+      </c>
+      <c r="AQ70" s="3">
         <v>4017500</v>
       </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1346000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1269400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1219300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1150200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1085100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-867400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-699100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-737500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-592700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-336000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-267900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-130600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-167400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-169000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-110200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-122600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-182200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-436100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-550400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-771100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-863700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-877900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-914800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-868000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-789100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-701200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-665600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-650200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-648400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-615300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-577400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-760300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-735100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-735800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-675700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-662400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-609400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-553500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-487600</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-494300</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4840300</v>
+      </c>
+      <c r="E76" s="3">
         <v>4874300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4898100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4962100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5022500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5216300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5362600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5260100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5357200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5598700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5663200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5757700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5715900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5695700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5723400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5677200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5604700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5348700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5235200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5002400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4872300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4805400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4766400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4794100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4857700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4948100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4997900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5007900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5031400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5044800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5094500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4870100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4870800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4866000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4915000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4911200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>4951600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4996000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>5044400</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>5042200</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>500000</v>
+      </c>
+      <c r="E81" s="3">
         <v>526300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>507100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>511100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>358400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>407800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>614600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>430300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>518100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>508900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>439300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>613300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>578000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>517700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>362600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2712200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>603400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>464100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>558100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>442300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>346200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>385800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>292200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>246900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>246100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>313100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>327300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>337400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>306400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>301700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>532700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>322700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>348300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>287800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>334100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>279700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>276700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>281100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>352800</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>309000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>262700</v>
+      </c>
+      <c r="E83" s="3">
         <v>259400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>256700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>253700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>252300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>249400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>246200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>222700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>211300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>207100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>209500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>200800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>194400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>188200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>226500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>220800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>218700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>222100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>205300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>188600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>172700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>146900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>141400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>138300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>137600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>135900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>134900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>129200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>126900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>121900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>121400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>124500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>119800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>118000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>120100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>113300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>110200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>110900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>111700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>109400</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>868400</v>
+      </c>
+      <c r="E89" s="3">
         <v>694800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>733600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>875100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>872700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>705100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>768600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>798800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>895300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>665600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>791700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>875700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>882400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>696900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>736400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>927000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>797500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>656200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>728800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>684300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>621300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>509200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>512600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>528300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>539100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>463000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>500000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>552500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>541600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>473600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>485300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>600400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>519400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>458500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>473200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>537200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>506200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>459100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>465300</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>515300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,8 +9910,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9734,86 +9955,89 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R91" s="3">
         <v>-432500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-498400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-311800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-288500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2383400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-471700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-54100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-36600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-37500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-43800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-74000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>79500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-58600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-15900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-40500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-47300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-11600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-118100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1025000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-152200</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-347000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-147300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-364300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-696000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-338300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-286500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-411600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-213300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-191100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-186600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-490200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2501000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-335000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-212300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-432500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2148300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-307300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-288500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2372400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-471400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2316000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-403700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-589600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-103300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-134900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-289900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-226700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-257500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-223600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-189500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-152200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-106900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-139800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-114900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-342700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-151800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-127300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-118100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-243600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-167800</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10266,35 +10500,35 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3">
         <v>-399900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2709100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-399900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-399600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-350900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-351200</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-350100</v>
       </c>
       <c r="X96" s="3">
         <v>-350100</v>
       </c>
       <c r="Y96" s="3">
+        <v>-350100</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-349900</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-349800</v>
       </c>
       <c r="AA96" s="3">
         <v>-349800</v>
@@ -10306,46 +10540,49 @@
         <v>-349800</v>
       </c>
       <c r="AD96" s="3">
+        <v>-349800</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-349700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-349600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-349500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-403300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-403200</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-403100</v>
       </c>
       <c r="AJ96" s="3">
         <v>-403100</v>
       </c>
       <c r="AK96" s="3">
+        <v>-403100</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-402800</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-409600</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-409700</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-408300</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-407000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-369700</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-396200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-731000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-347600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-987300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>283000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-578800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-508600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-559900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-432900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-577200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-561400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1603600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-591100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-564000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-410400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3205000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-416600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-161300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1420300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>264900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2015900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-203000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>41100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1399000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>146700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>135500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-404400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-114100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-179300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-423000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-402000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-399700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-404200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-413600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-397600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-49400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-141400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-403800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-77500</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-550500</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10870,69 +11119,69 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>-200</v>
-      </c>
-      <c r="T101" s="3">
-        <v>200</v>
       </c>
       <c r="U101" s="3">
         <v>200</v>
       </c>
       <c r="V101" s="3">
+        <v>200</v>
+      </c>
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>200</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-200</v>
       </c>
       <c r="Z101" s="3">
         <v>-200</v>
       </c>
       <c r="AA101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
         <v>0</v>
       </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>100</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-200</v>
       </c>
-      <c r="AI101" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
@@ -10940,140 +11189,146 @@
         <v>0</v>
       </c>
       <c r="AL101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AM101" s="3">
         <v>-100</v>
       </c>
       <c r="AN101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AO101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP101" s="3">
         <v>-200</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>125300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-183500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>21600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-808100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>817400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-160200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-151600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>25500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>271300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-98200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-260000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-21700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-43700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-79400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-106500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-129700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>73500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>206600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-223100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>477900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>321200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-97400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-36100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-974200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>550800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>308600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-131100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>180900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>142400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-142600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-71100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>93700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-24600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-70100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-267100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>336000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>237400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-62800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>144100</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-202900</v>
       </c>
     </row>
